--- a/Controle_GD_TriStarOne.xlsx
+++ b/Controle_GD_TriStarOne.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1LlAaT2nYKKYWkOQa-_3PdNIAaSpQrtVt\01. PROJETO PAINÉIS SOLARES\_TRI STAR ONE SCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE70D09B-662B-4029-8A15-CBDCBAB763BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EA21AD-C514-4ECD-B34A-DE09A48E61EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2955" windowWidth="29040" windowHeight="15720" tabRatio="814" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-2955" windowWidth="29040" windowHeight="15720" tabRatio="814" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,9 @@
     <sheet name="Auxiliar (Não Editar)" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Dados Mensais (Histórico)'!$A$4:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Dados Mensais (Histórico)'!$A$4:$P$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Rateio de Crédito'!$A$4:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Resumo Usinas (Histórico)'!$B$4:$N$22</definedName>
     <definedName name="CompetenciasDisponiveis">OFFSET('Resumo Usinas (Histórico)'!$G$5,0,0,COUNTIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;&gt;"),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="189">
   <si>
     <t>Instruções de Preenchimento — Controle GD TRI STAR ONE SCP</t>
   </si>
@@ -678,6 +680,12 @@
   <si>
     <t>Total Injetado até Competência referenciada (kWh)</t>
   </si>
+  <si>
+    <t xml:space="preserve"> 218723703243</t>
+  </si>
+  <si>
+    <t>99953603243</t>
+  </si>
 </sst>
 </file>
 
@@ -689,7 +697,7 @@
     <numFmt numFmtId="165" formatCode="[$R$-416]\ #,##0.00000000;[Red]\-[$R$-416]\ #,##0.00000000"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000000000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -848,12 +856,6 @@
       <sz val="8"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1053,7 +1055,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -1088,7 +1090,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1141,31 +1142,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1178,6 +1166,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1214,14 +1203,14 @@
     <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1243,12 +1232,64 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1695,7 +1736,7 @@
                   <c:v>8831</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3913</c:v>
+                  <c:v>7136</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9082</c:v>
@@ -2272,13 +2313,13 @@
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="36"/>
                 <c:pt idx="0">
-                  <c:v>579</c:v>
+                  <c:v>1158</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3334</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3223</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -3728,8 +3769,8 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>409575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3946,317 +3987,297 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
     </row>
     <row r="6" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
     </row>
     <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="72" t="s">
+      <c r="A12" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
     </row>
     <row r="13" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="72"/>
-      <c r="C13" s="72"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="72"/>
-      <c r="F13" s="72"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
     </row>
     <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="72" t="s">
+      <c r="A14" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
     </row>
     <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="73" t="s">
+      <c r="A17" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
     </row>
     <row r="18" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
     </row>
     <row r="19" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
     </row>
     <row r="20" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="72"/>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="72"/>
-      <c r="F21" s="72"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
     </row>
     <row r="22" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="72"/>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
     </row>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="72" t="s">
+      <c r="A25" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="B25" s="72"/>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
+      <c r="B25" s="62"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
     </row>
     <row r="26" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="72" t="s">
+      <c r="A27" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="72"/>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="72"/>
-      <c r="F27" s="72"/>
+      <c r="B27" s="62"/>
+      <c r="C27" s="62"/>
+      <c r="D27" s="62"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
     </row>
     <row r="28" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
+      <c r="D28" s="62"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="73" t="s">
+      <c r="A29" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="73"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="72" t="s">
+      <c r="A30" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="72"/>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
     </row>
     <row r="31" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="72" t="s">
+      <c r="A31" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
     </row>
     <row r="32" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="72" t="s">
+      <c r="A32" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
     </row>
     <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="72" t="s">
+      <c r="A33" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="72"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A32:F32"/>
@@ -4266,6 +4287,26 @@
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -32642,117 +32683,117 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0" style="18" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="2" max="2" width="29.85546875" style="18" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="11.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="18" customWidth="1"/>
-    <col min="7" max="7" width="15" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.42578125" style="18" customWidth="1"/>
-    <col min="10" max="13" width="8.7109375" style="18"/>
-    <col min="14" max="14" width="10.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.7109375" style="18"/>
+    <col min="1" max="1" width="0" style="17" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="2" width="29.85546875" style="17" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="11.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="15" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" style="17" customWidth="1"/>
+    <col min="10" max="13" width="8.7109375" style="17"/>
+    <col min="14" max="14" width="10.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
       <c r="E4" s="7">
         <v>46266</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="68"/>
-      <c r="I4" s="19" t="str">
-        <f>TEXT(_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;"),"mmm/AAAA")</f>
+      <c r="H4" s="55"/>
+      <c r="I4" s="18" t="str">
+        <f>TEXT(_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;"),"mmm/AAAA")</f>
         <v>set/2026</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="M5" s="20"/>
-      <c r="N5" s="21"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="20"/>
     </row>
     <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="56" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
-      <c r="F6" s="70" t="s">
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="F6" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="70"/>
-      <c r="I6" s="71" t="s">
+      <c r="G6" s="57"/>
+      <c r="I6" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="71"/>
+      <c r="J6" s="58"/>
     </row>
     <row r="7" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="61">
+      <c r="B7" s="48">
         <f>G22</f>
-        <v>30288</v>
-      </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="F7" s="62">
-        <f>H38</f>
-        <v>26375</v>
-      </c>
-      <c r="G7" s="62"/>
-      <c r="I7" s="63" t="s">
+        <v>33511</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="F7" s="49">
+        <f>H37</f>
+        <v>33511</v>
+      </c>
+      <c r="G7" s="49"/>
+      <c r="I7" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="J7" s="64"/>
+      <c r="J7" s="51"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>185</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -32781,7 +32822,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="str">
+      <c r="A12" s="17" t="str">
         <f>CONCATENATE(D12,E12)</f>
         <v>703010264346266</v>
       </c>
@@ -32791,23 +32832,23 @@
       <c r="C12" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="24">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D12,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D12,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E12" s="23">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D12,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D12,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>46266</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="24">
         <f>IF(E12="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(A12,'Resumo Usinas (Histórico)'!$A$5:$A$500,0)),"-"))</f>
         <v>30</v>
       </c>
-      <c r="G12" s="25">
-        <f>IF(E12="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$H$5:$H$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D12,'Resumo Usinas (Histórico)'!$G$5:$G$500,E12),"-"))</f>
+      <c r="G12" s="24">
+        <f>IF(E12="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$I$5:$I$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D12,'Resumo Usinas (Histórico)'!$G$5:$G$500,E12),"-"))</f>
         <v>8462</v>
       </c>
-      <c r="H12" s="26">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D12,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H12" s="25">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D12,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>1</v>
       </c>
       <c r="I12" s="9" t="s">
@@ -32815,7 +32856,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="str">
+      <c r="A13" s="17" t="str">
         <f t="shared" ref="A13:A21" si="0">CONCATENATE(D13,E13)</f>
         <v>703086904946266</v>
       </c>
@@ -32825,23 +32866,23 @@
       <c r="C13" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="24">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D13,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D13,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E13" s="23">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D13,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D13,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>46266</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <f>IF(E13="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(A13,'Resumo Usinas (Histórico)'!$A$5:$A$500,0)),"-"))</f>
         <v>33</v>
       </c>
-      <c r="G13" s="25">
-        <f>IF(E13="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$H$5:$H$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D13,'Resumo Usinas (Histórico)'!$G$5:$G$500,E13),"-"))</f>
+      <c r="G13" s="24">
+        <f>IF(E13="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$I$5:$I$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D13,'Resumo Usinas (Histórico)'!$G$5:$G$500,E13),"-"))</f>
         <v>8831</v>
       </c>
-      <c r="H13" s="26">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D13,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H13" s="25">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D13,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>1</v>
       </c>
       <c r="I13" s="9" t="s">
@@ -32849,9 +32890,9 @@
       </c>
     </row>
     <row r="14" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="str">
+      <c r="A14" s="17" t="str">
         <f t="shared" si="0"/>
-        <v>703086906546235</v>
+        <v>703086906546266</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>147</v>
@@ -32859,23 +32900,23 @@
       <c r="C14" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="90">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D14,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D14,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
-        <v>46235</v>
-      </c>
-      <c r="F14" s="25">
+      <c r="E14" s="23">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D14,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D14,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+        <v>46266</v>
+      </c>
+      <c r="F14" s="24">
         <f>IF(E14="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(A14,'Resumo Usinas (Histórico)'!$A$5:$A$500,0)),"-"))</f>
-        <v>15</v>
-      </c>
-      <c r="G14" s="25">
-        <f>IF(E14="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$H$5:$H$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D14,'Resumo Usinas (Histórico)'!$G$5:$G$500,E14),"-"))</f>
-        <v>3913</v>
-      </c>
-      <c r="H14" s="26">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D14,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+        <v>60</v>
+      </c>
+      <c r="G14" s="24">
+        <f>IF(E14="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$I$5:$I$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D14,'Resumo Usinas (Histórico)'!$G$5:$G$500,E14),"-"))</f>
+        <v>7136</v>
+      </c>
+      <c r="H14" s="25">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D14,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>1</v>
       </c>
       <c r="I14" s="9" t="s">
@@ -32883,7 +32924,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="str">
+      <c r="A15" s="17" t="str">
         <f t="shared" si="0"/>
         <v>703086929446266</v>
       </c>
@@ -32893,23 +32934,23 @@
       <c r="C15" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="24">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D15,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D15,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E15" s="23">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D15,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D15,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>46266</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <f>IF(E15="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(A15,'Resumo Usinas (Histórico)'!$A$5:$A$500,0)),"-"))</f>
         <v>60</v>
       </c>
-      <c r="G15" s="25">
-        <f>IF(E15="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$H$5:$H$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D15,'Resumo Usinas (Histórico)'!$G$5:$G$500,E15),"-"))</f>
+      <c r="G15" s="24">
+        <f>IF(E15="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$I$5:$I$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D15,'Resumo Usinas (Histórico)'!$G$5:$G$500,E15),"-"))</f>
         <v>9082</v>
       </c>
-      <c r="H15" s="26">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D15,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H15" s="25">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D15,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>1</v>
       </c>
       <c r="I15" s="9" t="s">
@@ -32917,7 +32958,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" ht="22.5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="str">
+      <c r="A16" s="17" t="str">
         <f t="shared" si="0"/>
         <v>A DEFINIR-05Sem dados</v>
       </c>
@@ -32925,23 +32966,23 @@
         <v>52</v>
       </c>
       <c r="C16" s="15"/>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="28" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D16,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D16,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E16" s="27" t="str">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D16,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D16,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>Sem dados</v>
       </c>
-      <c r="F16" s="29" t="str">
+      <c r="F16" s="28" t="str">
         <f>IF(E16="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(D16,'Resumo Usinas (Histórico)'!$C$5:$C$500,0)),"-"))</f>
         <v>-</v>
       </c>
-      <c r="G16" s="29" t="str">
-        <f>IF(E16="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D16,'Resumo Usinas (Histórico)'!$G$5:$G$500,E16),"-"))</f>
+      <c r="G16" s="28" t="str">
+        <f>IF(E16="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D16,'Resumo Usinas (Histórico)'!$G$5:$G$500,E16),"-"))</f>
         <v>-</v>
       </c>
-      <c r="H16" s="30">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D16,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H16" s="29">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D16,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>0</v>
       </c>
       <c r="I16" s="14" t="s">
@@ -32949,7 +32990,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="22.5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="str">
+      <c r="A17" s="17" t="str">
         <f t="shared" si="0"/>
         <v>A DEFINIR-06Sem dados</v>
       </c>
@@ -32957,23 +32998,23 @@
         <v>55</v>
       </c>
       <c r="C17" s="15"/>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="28" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D17,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D17,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E17" s="27" t="str">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D17,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D17,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>Sem dados</v>
       </c>
-      <c r="F17" s="29" t="str">
+      <c r="F17" s="28" t="str">
         <f>IF(E17="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(D17,'Resumo Usinas (Histórico)'!$C$5:$C$500,0)),"-"))</f>
         <v>-</v>
       </c>
-      <c r="G17" s="29" t="str">
-        <f>IF(E17="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D17,'Resumo Usinas (Histórico)'!$G$5:$G$500,E17),"-"))</f>
+      <c r="G17" s="28" t="str">
+        <f>IF(E17="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D17,'Resumo Usinas (Histórico)'!$G$5:$G$500,E17),"-"))</f>
         <v>-</v>
       </c>
-      <c r="H17" s="30">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D17,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H17" s="29">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D17,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>0</v>
       </c>
       <c r="I17" s="14" t="s">
@@ -32981,7 +33022,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="22.5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="str">
+      <c r="A18" s="17" t="str">
         <f t="shared" si="0"/>
         <v>A DEFINIR-07Sem dados</v>
       </c>
@@ -32989,23 +33030,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="15"/>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="28" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D18,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D18,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E18" s="27" t="str">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D18,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D18,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>Sem dados</v>
       </c>
-      <c r="F18" s="29" t="str">
+      <c r="F18" s="28" t="str">
         <f>IF(E18="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(D18,'Resumo Usinas (Histórico)'!$C$5:$C$500,0)),"-"))</f>
         <v>-</v>
       </c>
-      <c r="G18" s="29" t="str">
-        <f>IF(E18="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D18,'Resumo Usinas (Histórico)'!$G$5:$G$500,E18),"-"))</f>
+      <c r="G18" s="28" t="str">
+        <f>IF(E18="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D18,'Resumo Usinas (Histórico)'!$G$5:$G$500,E18),"-"))</f>
         <v>-</v>
       </c>
-      <c r="H18" s="30">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D18,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H18" s="29">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D18,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>0</v>
       </c>
       <c r="I18" s="14" t="s">
@@ -33013,7 +33054,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="22.5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="str">
+      <c r="A19" s="17" t="str">
         <f t="shared" si="0"/>
         <v>A DEFINIR-08Sem dados</v>
       </c>
@@ -33021,23 +33062,23 @@
         <v>59</v>
       </c>
       <c r="C19" s="15"/>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="28" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D19,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D19,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E19" s="27" t="str">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D19,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D19,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>Sem dados</v>
       </c>
-      <c r="F19" s="29" t="str">
+      <c r="F19" s="28" t="str">
         <f>IF(E19="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(D19,'Resumo Usinas (Histórico)'!$C$5:$C$500,0)),"-"))</f>
         <v>-</v>
       </c>
-      <c r="G19" s="29" t="str">
-        <f>IF(E19="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D19,'Resumo Usinas (Histórico)'!$G$5:$G$500,E19),"-"))</f>
+      <c r="G19" s="28" t="str">
+        <f>IF(E19="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D19,'Resumo Usinas (Histórico)'!$G$5:$G$500,E19),"-"))</f>
         <v>-</v>
       </c>
-      <c r="H19" s="30">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D19,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H19" s="29">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D19,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>0</v>
       </c>
       <c r="I19" s="14" t="s">
@@ -33045,7 +33086,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="22.5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="str">
+      <c r="A20" s="17" t="str">
         <f t="shared" si="0"/>
         <v>A DEFINIR-09Sem dados</v>
       </c>
@@ -33053,23 +33094,23 @@
         <v>61</v>
       </c>
       <c r="C20" s="15"/>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="28" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D20,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D20,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E20" s="27" t="str">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D20,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D20,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>Sem dados</v>
       </c>
-      <c r="F20" s="29" t="str">
+      <c r="F20" s="28" t="str">
         <f>IF(E20="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(D20,'Resumo Usinas (Histórico)'!$C$5:$C$500,0)),"-"))</f>
         <v>-</v>
       </c>
-      <c r="G20" s="29" t="str">
-        <f>IF(E20="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D20,'Resumo Usinas (Histórico)'!$G$5:$G$500,E20),"-"))</f>
+      <c r="G20" s="28" t="str">
+        <f>IF(E20="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D20,'Resumo Usinas (Histórico)'!$G$5:$G$500,E20),"-"))</f>
         <v>-</v>
       </c>
-      <c r="H20" s="30">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D20,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H20" s="29">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D20,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>0</v>
       </c>
       <c r="I20" s="14" t="s">
@@ -33077,7 +33118,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="22.5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="str">
+      <c r="A21" s="17" t="str">
         <f t="shared" si="0"/>
         <v>A DEFINIR-10Sem dados</v>
       </c>
@@ -33085,23 +33126,23 @@
         <v>63</v>
       </c>
       <c r="C21" s="15"/>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="28" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D21,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D21,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
+      <c r="E21" s="27" t="str">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,D21,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")=0,"Sem dados",_xlfn.MAXIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D21,'Resumo Usinas (Histórico)'!$G$5:$G$500,"&lt;="&amp;$E$4))</f>
         <v>Sem dados</v>
       </c>
-      <c r="F21" s="29" t="str">
+      <c r="F21" s="28" t="str">
         <f>IF(E21="Sem dados","-",IFERROR(INDEX('Resumo Usinas (Histórico)'!$D$5:$D$500,MATCH(D21,'Resumo Usinas (Histórico)'!$C$5:$C$500,0)),"-"))</f>
         <v>-</v>
       </c>
-      <c r="G21" s="29" t="str">
-        <f>IF(E21="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D21,'Resumo Usinas (Histórico)'!$G$5:$G$500,E21),"-"))</f>
+      <c r="G21" s="28" t="str">
+        <f>IF(E21="Sem dados","-",IFERROR(SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,D21,'Resumo Usinas (Histórico)'!$G$5:$G$500,E21),"-"))</f>
         <v>-</v>
       </c>
-      <c r="H21" s="30">
-        <f>IFERROR(SUMIFS('Rateio de Crédito'!$E$5:$E$150,'Rateio de Crédito'!$B$5:$B$150,D21,'Rateio de Crédito'!$D$5:$D$150,"&lt;&gt;Injetor (Gerador)"),0)</f>
+      <c r="H21" s="29">
+        <f>IFERROR(SUMIFS('Rateio de Crédito'!$F$5:$F$151,'Rateio de Crédito'!$B$5:$B$151,D21,'Rateio de Crédito'!$E$5:$E$151,"&lt;&gt;Injetor (Gerador)"),0)</f>
         <v>0</v>
       </c>
       <c r="I21" s="14" t="s">
@@ -33109,25 +33150,25 @@
       </c>
     </row>
     <row r="22" spans="1:9" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="33">
+      <c r="C22" s="30"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32">
         <f>SUM(G12:G21)</f>
-        <v>30288</v>
-      </c>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
+        <v>33511</v>
+      </c>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="21"/>
     </row>
     <row r="26" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B26" s="8" t="s">
@@ -33162,25 +33203,25 @@
       <c r="C27" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="22" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="26">
-        <f>'Rateio de Crédito'!E6</f>
+      <c r="G27" s="25">
+        <f>VLOOKUP(E27,'Rateio de Crédito'!C:F,4,0)</f>
         <v>1</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="24">
         <f>IFERROR(G27*$G$12,"-")</f>
         <v>8462</v>
       </c>
-      <c r="I27" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F6),"-",'Rateio de Crédito'!F6)</f>
+      <c r="I27" s="23">
+        <f>IF(ISBLANK('Rateio de Crédito'!G6),"-",'Rateio de Crédito'!G6)</f>
         <v>46204</v>
       </c>
     </row>
@@ -33191,55 +33232,55 @@
       <c r="C28" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="22" t="s">
         <v>45</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G28" s="26">
-        <f>'Rateio de Crédito'!E7</f>
+      <c r="G28" s="25">
+        <f>VLOOKUP(E28,'Rateio de Crédito'!C:F,4,0)</f>
         <v>1</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="24">
         <f>IFERROR(G28*$G$13,"-")</f>
         <v>8831</v>
       </c>
-      <c r="I28" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F7),"-",'Rateio de Crédito'!F7)</f>
+      <c r="I28" s="23">
+        <f>IF(ISBLANK('Rateio de Crédito'!G7),"-",'Rateio de Crédito'!G7)</f>
         <v>46204</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>48</v>
+      <c r="E29" s="22" t="s">
+        <v>172</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="26">
-        <f>'Rateio de Crédito'!E8</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="25">
+        <v>74</v>
+      </c>
+      <c r="G29" s="25">
+        <f>VLOOKUP(E29,'Rateio de Crédito'!C:F,4,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="24">
         <f>IFERROR(G29*$G$14,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F8),"-",'Rateio de Crédito'!F8)</f>
-        <v>46235</v>
+        <v>7136</v>
+      </c>
+      <c r="I29" s="23">
+        <f>IF(ISBLANK('Rateio de Crédito'!G10),"-",'Rateio de Crédito'!G10)</f>
+        <v>46204</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -33249,25 +33290,25 @@
       <c r="C30" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="22" t="s">
         <v>76</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G30" s="26">
-        <f>'Rateio de Crédito'!E10</f>
+      <c r="G30" s="25">
+        <f>VLOOKUP(E30,'Rateio de Crédito'!C:F,4,0)</f>
         <v>0.25</v>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="24">
         <f>IFERROR(G30*$G$15,"-")</f>
         <v>2270.5</v>
       </c>
-      <c r="I30" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F10),"-",'Rateio de Crédito'!F10)</f>
+      <c r="I30" s="23">
+        <f>IF(ISBLANK('Rateio de Crédito'!G12),"-",'Rateio de Crédito'!G12)</f>
         <v>46204</v>
       </c>
     </row>
@@ -33278,25 +33319,25 @@
       <c r="C31" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="22" t="s">
         <v>77</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G31" s="26">
-        <f>'Rateio de Crédito'!E11</f>
+      <c r="G31" s="25">
+        <f>VLOOKUP(E31,'Rateio de Crédito'!C:F,4,0)</f>
         <v>0.25</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="24">
         <f>IFERROR(G31*$G$15,"-")</f>
         <v>2270.5</v>
       </c>
-      <c r="I31" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F11),"-",'Rateio de Crédito'!F11)</f>
+      <c r="I31" s="23">
+        <f>IF(ISBLANK('Rateio de Crédito'!G13),"-",'Rateio de Crédito'!G13)</f>
         <v>46204</v>
       </c>
     </row>
@@ -33307,25 +33348,25 @@
       <c r="C32" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="22" t="s">
         <v>78</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G32" s="26">
-        <f>'Rateio de Crédito'!E12</f>
+      <c r="G32" s="25">
+        <f>VLOOKUP(E32,'Rateio de Crédito'!C:F,4,0)</f>
         <v>0.25</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="24">
         <f>IFERROR(G32*$G$15,"-")</f>
         <v>2270.5</v>
       </c>
-      <c r="I32" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F12),"-",'Rateio de Crédito'!F12)</f>
+      <c r="I32" s="23">
+        <f>IF(ISBLANK('Rateio de Crédito'!G14),"-",'Rateio de Crédito'!G14)</f>
         <v>46204</v>
       </c>
     </row>
@@ -33336,154 +33377,120 @@
       <c r="C33" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="22" t="s">
         <v>79</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G33" s="26">
-        <f>'Rateio de Crédito'!E13</f>
+      <c r="G33" s="25">
+        <f>VLOOKUP(E33,'Rateio de Crédito'!C:F,4,0)</f>
         <v>0.25</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="24">
         <f>IFERROR(G33*$G$15,"-")</f>
         <v>2270.5</v>
       </c>
-      <c r="I33" s="24">
-        <f>IF(ISBLANK('Rateio de Crédito'!F13),"-",'Rateio de Crédito'!F13)</f>
-        <v>46204</v>
+      <c r="I33" s="23" t="str">
+        <f>IF(ISBLANK('Rateio de Crédito'!G15),"-",'Rateio de Crédito'!G15)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="34" spans="2:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B34" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="27"/>
+        <v>55</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="26"/>
       <c r="F34" s="14"/>
-      <c r="G34" s="30">
-        <f>'Rateio de Crédito'!E14</f>
-        <v>1</v>
-      </c>
-      <c r="H34" s="29" t="str">
-        <f>IFERROR(G34*$G$16,"-")</f>
+      <c r="G34" s="25"/>
+      <c r="H34" s="28" t="str">
+        <f>IFERROR(G34*$G$17,"-")</f>
         <v>-</v>
       </c>
-      <c r="I34" s="28">
-        <f>IF(ISBLANK('Rateio de Crédito'!F14),"-",'Rateio de Crédito'!F14)</f>
-        <v>46235</v>
+      <c r="I34" s="27" t="str">
+        <f>IF(ISBLANK('Rateio de Crédito'!G16),"-",'Rateio de Crédito'!G16)</f>
+        <v>-</v>
       </c>
     </row>
     <row r="35" spans="2:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B35" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E35" s="27"/>
+        <v>57</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="26"/>
       <c r="F35" s="14"/>
-      <c r="G35" s="30">
-        <f>'Rateio de Crédito'!E15</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="29" t="str">
-        <f>IFERROR(G35*$G$17,"-")</f>
+      <c r="G35" s="25"/>
+      <c r="H35" s="28" t="str">
+        <f>IFERROR(G35*$G$18,"-")</f>
         <v>-</v>
       </c>
-      <c r="I35" s="28" t="str">
-        <f>IF(ISBLANK('Rateio de Crédito'!F15),"-",'Rateio de Crédito'!F15)</f>
+      <c r="I35" s="27" t="str">
+        <f>IF(ISBLANK('Rateio de Crédito'!G17),"-",'Rateio de Crédito'!G17)</f>
         <v>-</v>
       </c>
     </row>
     <row r="36" spans="2:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B36" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" s="27"/>
+        <v>59</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="26"/>
       <c r="F36" s="14"/>
-      <c r="G36" s="30">
-        <f>'Rateio de Crédito'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="29" t="str">
-        <f>IFERROR(G36*$G$18,"-")</f>
+      <c r="G36" s="25"/>
+      <c r="H36" s="28" t="str">
+        <f>IFERROR(G36*$G$19,"-")</f>
         <v>-</v>
       </c>
-      <c r="I36" s="28" t="str">
-        <f>IF(ISBLANK('Rateio de Crédito'!F16),"-",'Rateio de Crédito'!F16)</f>
+      <c r="I36" s="27" t="str">
+        <f>IF(ISBLANK('Rateio de Crédito'!G18),"-",'Rateio de Crédito'!G18)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="37" spans="2:9" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="E37" s="27"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="30">
-        <f>'Rateio de Crédito'!E17</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="29" t="str">
-        <f>IFERROR(G37*$G$19,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I37" s="28" t="str">
-        <f>IF(ISBLANK('Rateio de Crédito'!F17),"-",'Rateio de Crédito'!F17)</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="31" t="s">
+    <row r="37" spans="2:9" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="33">
-        <f>SUM(H27:H37)</f>
-        <v>26375</v>
-      </c>
-      <c r="I38" s="32"/>
-    </row>
-    <row r="40" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="65" t="s">
+      <c r="C37" s="30"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="32">
+        <f>SUM(H27:H36)</f>
+        <v>33511</v>
+      </c>
+      <c r="I37" s="31"/>
+    </row>
+    <row r="39" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="65"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="65"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -33491,7 +33498,7 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B39:I39"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="G4:H4"/>
@@ -33519,84 +33526,84 @@
   <dimension ref="A1:Q42"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="34" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.7109375" style="34" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="2.7109375" style="34" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" style="34"/>
-    <col min="16" max="16" width="12.85546875" style="34" customWidth="1"/>
-    <col min="17" max="17" width="68.7109375" style="34" customWidth="1"/>
-    <col min="18" max="16384" width="8.7109375" style="34"/>
+    <col min="1" max="1" width="14" style="33" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.7109375" style="33" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.7109375" style="33" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" style="33"/>
+    <col min="16" max="16" width="12.85546875" style="33" customWidth="1"/>
+    <col min="17" max="17" width="68.7109375" style="33" customWidth="1"/>
+    <col min="18" max="16384" width="8.7109375" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="65" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="56"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="J3" s="80" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="J3" s="67" t="s">
         <v>152</v>
       </c>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="76" t="s">
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="P3" s="57" t="s">
+      <c r="P3" s="43" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J4" s="54">
+      <c r="J4" s="40">
         <v>7030102643</v>
       </c>
-      <c r="K4" s="54">
+      <c r="K4" s="40">
         <v>7030869049</v>
       </c>
-      <c r="L4" s="54">
+      <c r="L4" s="40">
         <v>7030869065</v>
       </c>
-      <c r="M4" s="54">
+      <c r="M4" s="40">
         <v>7030869294</v>
       </c>
-      <c r="N4" s="76"/>
-      <c r="P4" s="57" t="s">
+      <c r="N4" s="63"/>
+      <c r="P4" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="Q4" s="34" t="s">
+      <c r="Q4" s="33" t="s">
         <v>158</v>
       </c>
     </row>
@@ -33616,23 +33623,23 @@
       <c r="E5" s="8">
         <v>7030869294</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="J5" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="K5" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="L5" s="54" t="s">
+      <c r="L5" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="M5" s="54" t="s">
+      <c r="M5" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="N5" s="76"/>
-      <c r="P5" s="57" t="s">
+      <c r="N5" s="63"/>
+      <c r="P5" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="Q5" s="34" t="s">
+      <c r="Q5" s="33" t="s">
         <v>160</v>
       </c>
     </row>
@@ -33652,58 +33659,58 @@
       <c r="E6" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="G6" s="54" t="s">
+      <c r="G6" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="54" t="s">
+      <c r="H6" s="40" t="s">
         <v>151</v>
       </c>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="K6" s="54" t="s">
+      <c r="K6" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="L6" s="54" t="s">
+      <c r="L6" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="M6" s="54" t="s">
+      <c r="M6" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="N6" s="77"/>
-      <c r="P6" s="57" t="s">
+      <c r="N6" s="64"/>
+      <c r="P6" s="43" t="s">
         <v>161</v>
       </c>
-      <c r="Q6" s="34" t="s">
+      <c r="Q6" s="33" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
-        <f>_xlfn.MINIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")</f>
+        <f>_xlfn.MINIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")</f>
         <v>46204</v>
       </c>
       <c r="B7" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7))</f>
         <v>338</v>
       </c>
       <c r="C7" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7))</f>
         <v>875</v>
       </c>
       <c r="D7" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7))</f>
-        <v>579</v>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7))</f>
+        <v>1158</v>
       </c>
       <c r="E7" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A7))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A7))</f>
         <v>608</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="41">
         <f>'Preco (R$ x KWh)'!B26</f>
         <v>1.0319782800000001</v>
       </c>
-      <c r="H7" s="55">
+      <c r="H7" s="41">
         <f>G7*0.7</f>
         <v>0.72238479600000005</v>
       </c>
@@ -33717,7 +33724,7 @@
       </c>
       <c r="L7" s="13">
         <f t="shared" si="0"/>
-        <v>418.26</v>
+        <v>836.52</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="0"/>
@@ -33725,9 +33732,9 @@
       </c>
       <c r="N7" s="13">
         <f>SUM(J7:M7)</f>
-        <v>1733.73</v>
-      </c>
-      <c r="P7" s="57"/>
+        <v>2151.9899999999998</v>
+      </c>
+      <c r="P7" s="43"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
@@ -33735,26 +33742,26 @@
         <v>46235</v>
       </c>
       <c r="B8" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8))</f>
         <v>3425</v>
       </c>
       <c r="C8" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8))</f>
         <v>3585</v>
       </c>
       <c r="D8" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8))</f>
         <v>3334</v>
       </c>
       <c r="E8" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A8))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A8))</f>
         <v>3322</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="41">
         <f>'Preco (R$ x KWh)'!B27</f>
         <v>1.0347311000000001</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="41">
         <f t="shared" ref="H8:H42" si="2">G8*0.7</f>
         <v>0.72431177000000002</v>
       </c>
@@ -33778,10 +33785,10 @@
         <f t="shared" ref="N8:N42" si="7">SUM(J8:M8)</f>
         <v>9898.4500000000007</v>
       </c>
-      <c r="P8" s="57" t="s">
+      <c r="P8" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="Q8" s="58" t="s">
+      <c r="Q8" s="44" t="s">
         <v>167</v>
       </c>
     </row>
@@ -33791,26 +33798,26 @@
         <v>46266</v>
       </c>
       <c r="B9" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9))</f>
         <v>4699</v>
       </c>
       <c r="C9" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9))</f>
         <v>4371</v>
       </c>
-      <c r="D9" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9))</f>
-        <v/>
+      <c r="D9" s="13">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9))</f>
+        <v>3223</v>
       </c>
       <c r="E9" s="13">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A9))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A9))</f>
         <v>5152</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="41">
         <f>'Preco (R$ x KWh)'!B28</f>
         <v>1.0448766199999999</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="41">
         <f t="shared" si="2"/>
         <v>0.73141363399999992</v>
       </c>
@@ -33822,9 +33829,9 @@
         <f t="shared" si="4"/>
         <v>3197.01</v>
       </c>
-      <c r="L9" s="13" t="str">
+      <c r="L9" s="13">
         <f t="shared" si="5"/>
-        <v/>
+        <v>2357.35</v>
       </c>
       <c r="M9" s="13">
         <f t="shared" si="6"/>
@@ -33832,12 +33839,12 @@
       </c>
       <c r="N9" s="13">
         <f t="shared" si="7"/>
-        <v>10402.16</v>
-      </c>
-      <c r="P9" s="59" t="s">
+        <v>12759.51</v>
+      </c>
+      <c r="P9" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="Q9" s="58" t="s">
+      <c r="Q9" s="44" t="s">
         <v>183</v>
       </c>
     </row>
@@ -33847,26 +33854,26 @@
         <v>46296</v>
       </c>
       <c r="B10" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10))</f>
         <v/>
       </c>
       <c r="C10" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10))</f>
         <v/>
       </c>
       <c r="D10" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10))</f>
         <v/>
       </c>
       <c r="E10" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="41">
         <f>'Preco (R$ x KWh)'!B29</f>
         <v>0</v>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -33890,10 +33897,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="P10" s="57" t="s">
+      <c r="P10" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="Q10" s="34" t="s">
+      <c r="Q10" s="33" t="s">
         <v>166</v>
       </c>
     </row>
@@ -33903,26 +33910,26 @@
         <v>46327</v>
       </c>
       <c r="B11" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11))</f>
         <v/>
       </c>
       <c r="C11" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11))</f>
         <v/>
       </c>
       <c r="D11" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11))</f>
         <v/>
       </c>
       <c r="E11" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="41">
         <f>'Preco (R$ x KWh)'!B30</f>
         <v>0</v>
       </c>
-      <c r="H11" s="55">
+      <c r="H11" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -33953,26 +33960,26 @@
         <v>46357</v>
       </c>
       <c r="B12" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12))</f>
         <v/>
       </c>
       <c r="C12" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12))</f>
         <v/>
       </c>
       <c r="D12" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12))</f>
         <v/>
       </c>
       <c r="E12" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="41">
         <f>'Preco (R$ x KWh)'!B31</f>
         <v>0</v>
       </c>
-      <c r="H12" s="55">
+      <c r="H12" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34003,26 +34010,26 @@
         <v>46388</v>
       </c>
       <c r="B13" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13))</f>
         <v/>
       </c>
       <c r="C13" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13))</f>
         <v/>
       </c>
       <c r="D13" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13))</f>
         <v/>
       </c>
       <c r="E13" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="41">
         <f>'Preco (R$ x KWh)'!B32</f>
         <v>0</v>
       </c>
-      <c r="H13" s="55">
+      <c r="H13" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34053,26 +34060,26 @@
         <v>46419</v>
       </c>
       <c r="B14" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14))</f>
         <v/>
       </c>
       <c r="C14" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14))</f>
         <v/>
       </c>
       <c r="D14" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14))</f>
         <v/>
       </c>
       <c r="E14" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="41">
         <f>'Preco (R$ x KWh)'!B33</f>
         <v>0</v>
       </c>
-      <c r="H14" s="55">
+      <c r="H14" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34103,26 +34110,26 @@
         <v>46447</v>
       </c>
       <c r="B15" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15))</f>
         <v/>
       </c>
       <c r="C15" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15))</f>
         <v/>
       </c>
       <c r="D15" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15))</f>
         <v/>
       </c>
       <c r="E15" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="41">
         <f>'Preco (R$ x KWh)'!B34</f>
         <v>0</v>
       </c>
-      <c r="H15" s="55">
+      <c r="H15" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34153,26 +34160,26 @@
         <v>46478</v>
       </c>
       <c r="B16" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16))</f>
         <v/>
       </c>
       <c r="C16" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16))</f>
         <v/>
       </c>
       <c r="D16" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16))</f>
         <v/>
       </c>
       <c r="E16" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="41">
         <f>'Preco (R$ x KWh)'!B35</f>
         <v>0</v>
       </c>
-      <c r="H16" s="55">
+      <c r="H16" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34203,26 +34210,26 @@
         <v>46508</v>
       </c>
       <c r="B17" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17))</f>
         <v/>
       </c>
       <c r="C17" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17))</f>
         <v/>
       </c>
       <c r="D17" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17))</f>
         <v/>
       </c>
       <c r="E17" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="41">
         <f>'Preco (R$ x KWh)'!B36</f>
         <v>0</v>
       </c>
-      <c r="H17" s="55">
+      <c r="H17" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34253,26 +34260,26 @@
         <v>46539</v>
       </c>
       <c r="B18" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18))</f>
         <v/>
       </c>
       <c r="C18" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18))</f>
         <v/>
       </c>
       <c r="D18" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18))</f>
         <v/>
       </c>
       <c r="E18" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A18))</f>
-        <v/>
-      </c>
-      <c r="G18" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="41">
         <f>'Preco (R$ x KWh)'!B37</f>
         <v>0</v>
       </c>
-      <c r="H18" s="55">
+      <c r="H18" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34303,26 +34310,26 @@
         <v>46569</v>
       </c>
       <c r="B19" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19))</f>
         <v/>
       </c>
       <c r="C19" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19))</f>
         <v/>
       </c>
       <c r="D19" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19))</f>
         <v/>
       </c>
       <c r="E19" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="41">
         <f>'Preco (R$ x KWh)'!B38</f>
         <v>0</v>
       </c>
-      <c r="H19" s="55">
+      <c r="H19" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34353,26 +34360,26 @@
         <v>46600</v>
       </c>
       <c r="B20" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20))</f>
         <v/>
       </c>
       <c r="C20" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20))</f>
         <v/>
       </c>
       <c r="D20" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20))</f>
         <v/>
       </c>
       <c r="E20" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A20))</f>
-        <v/>
-      </c>
-      <c r="G20" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="41">
         <f>'Preco (R$ x KWh)'!B39</f>
         <v>0</v>
       </c>
-      <c r="H20" s="55">
+      <c r="H20" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34403,26 +34410,26 @@
         <v>46631</v>
       </c>
       <c r="B21" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21))</f>
         <v/>
       </c>
       <c r="C21" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21))</f>
         <v/>
       </c>
       <c r="D21" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21))</f>
         <v/>
       </c>
       <c r="E21" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A21))</f>
-        <v/>
-      </c>
-      <c r="G21" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="41">
         <f>'Preco (R$ x KWh)'!B40</f>
         <v>0</v>
       </c>
-      <c r="H21" s="55">
+      <c r="H21" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34453,26 +34460,26 @@
         <v>46661</v>
       </c>
       <c r="B22" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22))</f>
         <v/>
       </c>
       <c r="C22" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22))</f>
         <v/>
       </c>
       <c r="D22" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22))</f>
         <v/>
       </c>
       <c r="E22" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A22))</f>
-        <v/>
-      </c>
-      <c r="G22" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="41">
         <f>'Preco (R$ x KWh)'!B41</f>
         <v>0</v>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34503,26 +34510,26 @@
         <v>46692</v>
       </c>
       <c r="B23" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23))</f>
         <v/>
       </c>
       <c r="C23" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23))</f>
         <v/>
       </c>
       <c r="D23" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23))</f>
         <v/>
       </c>
       <c r="E23" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A23))</f>
-        <v/>
-      </c>
-      <c r="G23" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="41">
         <f>'Preco (R$ x KWh)'!B42</f>
         <v>0</v>
       </c>
-      <c r="H23" s="55">
+      <c r="H23" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34553,26 +34560,26 @@
         <v>46722</v>
       </c>
       <c r="B24" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24))</f>
         <v/>
       </c>
       <c r="C24" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24))</f>
         <v/>
       </c>
       <c r="D24" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24))</f>
         <v/>
       </c>
       <c r="E24" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A24))</f>
-        <v/>
-      </c>
-      <c r="G24" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="41">
         <f>'Preco (R$ x KWh)'!B43</f>
         <v>0</v>
       </c>
-      <c r="H24" s="55">
+      <c r="H24" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34603,26 +34610,26 @@
         <v>46753</v>
       </c>
       <c r="B25" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25))</f>
         <v/>
       </c>
       <c r="C25" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25))</f>
         <v/>
       </c>
       <c r="D25" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25))</f>
         <v/>
       </c>
       <c r="E25" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A25))</f>
-        <v/>
-      </c>
-      <c r="G25" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="41">
         <f>'Preco (R$ x KWh)'!B44</f>
         <v>0</v>
       </c>
-      <c r="H25" s="55">
+      <c r="H25" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34653,26 +34660,26 @@
         <v>46784</v>
       </c>
       <c r="B26" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26))</f>
         <v/>
       </c>
       <c r="C26" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26))</f>
         <v/>
       </c>
       <c r="D26" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26))</f>
         <v/>
       </c>
       <c r="E26" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A26))</f>
-        <v/>
-      </c>
-      <c r="G26" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="41">
         <f>'Preco (R$ x KWh)'!B45</f>
         <v>0</v>
       </c>
-      <c r="H26" s="55">
+      <c r="H26" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34703,26 +34710,26 @@
         <v>46813</v>
       </c>
       <c r="B27" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27))</f>
         <v/>
       </c>
       <c r="C27" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27))</f>
         <v/>
       </c>
       <c r="D27" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27))</f>
         <v/>
       </c>
       <c r="E27" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A27))</f>
-        <v/>
-      </c>
-      <c r="G27" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="41">
         <f>'Preco (R$ x KWh)'!B46</f>
         <v>0</v>
       </c>
-      <c r="H27" s="55">
+      <c r="H27" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34753,26 +34760,26 @@
         <v>46844</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28))</f>
         <v/>
       </c>
       <c r="C28" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28))</f>
         <v/>
       </c>
       <c r="D28" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28))</f>
         <v/>
       </c>
       <c r="E28" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A28))</f>
-        <v/>
-      </c>
-      <c r="G28" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="41">
         <f>'Preco (R$ x KWh)'!B47</f>
         <v>0</v>
       </c>
-      <c r="H28" s="55">
+      <c r="H28" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34803,26 +34810,26 @@
         <v>46874</v>
       </c>
       <c r="B29" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29))</f>
         <v/>
       </c>
       <c r="C29" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29))</f>
         <v/>
       </c>
       <c r="D29" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29))</f>
         <v/>
       </c>
       <c r="E29" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A29))</f>
-        <v/>
-      </c>
-      <c r="G29" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="41">
         <f>'Preco (R$ x KWh)'!B48</f>
         <v>0</v>
       </c>
-      <c r="H29" s="55">
+      <c r="H29" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34853,26 +34860,26 @@
         <v>46905</v>
       </c>
       <c r="B30" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30))</f>
         <v/>
       </c>
       <c r="C30" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30))</f>
         <v/>
       </c>
       <c r="D30" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30))</f>
         <v/>
       </c>
       <c r="E30" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A30))</f>
-        <v/>
-      </c>
-      <c r="G30" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="41">
         <f>'Preco (R$ x KWh)'!B49</f>
         <v>0</v>
       </c>
-      <c r="H30" s="55">
+      <c r="H30" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34903,26 +34910,26 @@
         <v>46935</v>
       </c>
       <c r="B31" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31))</f>
         <v/>
       </c>
       <c r="C31" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31))</f>
         <v/>
       </c>
       <c r="D31" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31))</f>
         <v/>
       </c>
       <c r="E31" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A31))</f>
-        <v/>
-      </c>
-      <c r="G31" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A31))</f>
+        <v/>
+      </c>
+      <c r="G31" s="41">
         <f>'Preco (R$ x KWh)'!B50</f>
         <v>0</v>
       </c>
-      <c r="H31" s="55">
+      <c r="H31" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34953,26 +34960,26 @@
         <v>46966</v>
       </c>
       <c r="B32" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32))</f>
         <v/>
       </c>
       <c r="C32" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32))</f>
         <v/>
       </c>
       <c r="D32" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32))</f>
         <v/>
       </c>
       <c r="E32" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A32))</f>
-        <v/>
-      </c>
-      <c r="G32" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A32))</f>
+        <v/>
+      </c>
+      <c r="G32" s="41">
         <f>'Preco (R$ x KWh)'!B51</f>
         <v>0</v>
       </c>
-      <c r="H32" s="55">
+      <c r="H32" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35003,26 +35010,26 @@
         <v>46997</v>
       </c>
       <c r="B33" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33))</f>
         <v/>
       </c>
       <c r="C33" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33))</f>
         <v/>
       </c>
       <c r="D33" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33))</f>
         <v/>
       </c>
       <c r="E33" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A33))</f>
-        <v/>
-      </c>
-      <c r="G33" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A33))</f>
+        <v/>
+      </c>
+      <c r="G33" s="41">
         <f>'Preco (R$ x KWh)'!B52</f>
         <v>0</v>
       </c>
-      <c r="H33" s="55">
+      <c r="H33" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35053,26 +35060,26 @@
         <v>47027</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34))</f>
         <v/>
       </c>
       <c r="C34" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34))</f>
         <v/>
       </c>
       <c r="D34" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34))</f>
         <v/>
       </c>
       <c r="E34" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A34))</f>
+        <v/>
+      </c>
+      <c r="G34" s="41">
         <f>'Preco (R$ x KWh)'!B53</f>
         <v>0</v>
       </c>
-      <c r="H34" s="55">
+      <c r="H34" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35103,26 +35110,26 @@
         <v>47058</v>
       </c>
       <c r="B35" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35))</f>
         <v/>
       </c>
       <c r="C35" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35))</f>
         <v/>
       </c>
       <c r="D35" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35))</f>
         <v/>
       </c>
       <c r="E35" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A35))</f>
-        <v/>
-      </c>
-      <c r="G35" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="41">
         <f>'Preco (R$ x KWh)'!B54</f>
         <v>0</v>
       </c>
-      <c r="H35" s="55">
+      <c r="H35" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35153,26 +35160,26 @@
         <v>47088</v>
       </c>
       <c r="B36" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36))</f>
         <v/>
       </c>
       <c r="C36" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36))</f>
         <v/>
       </c>
       <c r="D36" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36))</f>
         <v/>
       </c>
       <c r="E36" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A36))</f>
+        <v/>
+      </c>
+      <c r="G36" s="41">
         <f>'Preco (R$ x KWh)'!B55</f>
         <v>0</v>
       </c>
-      <c r="H36" s="55">
+      <c r="H36" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35203,26 +35210,26 @@
         <v>47119</v>
       </c>
       <c r="B37" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37))</f>
         <v/>
       </c>
       <c r="C37" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37))</f>
         <v/>
       </c>
       <c r="D37" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37))</f>
         <v/>
       </c>
       <c r="E37" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A37))</f>
-        <v/>
-      </c>
-      <c r="G37" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="41">
         <f>'Preco (R$ x KWh)'!B56</f>
         <v>0</v>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35253,26 +35260,26 @@
         <v>47150</v>
       </c>
       <c r="B38" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38))</f>
         <v/>
       </c>
       <c r="C38" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38))</f>
         <v/>
       </c>
       <c r="D38" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38))</f>
         <v/>
       </c>
       <c r="E38" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A38))</f>
-        <v/>
-      </c>
-      <c r="G38" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A38))</f>
+        <v/>
+      </c>
+      <c r="G38" s="41">
         <f>'Preco (R$ x KWh)'!B57</f>
         <v>0</v>
       </c>
-      <c r="H38" s="55">
+      <c r="H38" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35303,26 +35310,26 @@
         <v>47178</v>
       </c>
       <c r="B39" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39))</f>
         <v/>
       </c>
       <c r="C39" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39))</f>
         <v/>
       </c>
       <c r="D39" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39))</f>
         <v/>
       </c>
       <c r="E39" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A39))</f>
-        <v/>
-      </c>
-      <c r="G39" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A39))</f>
+        <v/>
+      </c>
+      <c r="G39" s="41">
         <f>'Preco (R$ x KWh)'!B58</f>
         <v>0</v>
       </c>
-      <c r="H39" s="55">
+      <c r="H39" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35353,26 +35360,26 @@
         <v>47209</v>
       </c>
       <c r="B40" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40))</f>
         <v/>
       </c>
       <c r="C40" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40))</f>
         <v/>
       </c>
       <c r="D40" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40))</f>
         <v/>
       </c>
       <c r="E40" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A40))</f>
-        <v/>
-      </c>
-      <c r="G40" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A40))</f>
+        <v/>
+      </c>
+      <c r="G40" s="41">
         <f>'Preco (R$ x KWh)'!B59</f>
         <v>0</v>
       </c>
-      <c r="H40" s="55">
+      <c r="H40" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35403,26 +35410,26 @@
         <v>47239</v>
       </c>
       <c r="B41" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41))</f>
         <v/>
       </c>
       <c r="C41" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41))</f>
         <v/>
       </c>
       <c r="D41" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41))</f>
         <v/>
       </c>
       <c r="E41" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A41))</f>
-        <v/>
-      </c>
-      <c r="G41" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A41))</f>
+        <v/>
+      </c>
+      <c r="G41" s="41">
         <f>'Preco (R$ x KWh)'!B60</f>
         <v>0</v>
       </c>
-      <c r="H41" s="55">
+      <c r="H41" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35453,26 +35460,26 @@
         <v>47270</v>
       </c>
       <c r="B42" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,B$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,B$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42))</f>
         <v/>
       </c>
       <c r="C42" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,C$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,C$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42))</f>
         <v/>
       </c>
       <c r="D42" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,D$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42))</f>
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,D$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42))</f>
         <v/>
       </c>
       <c r="E42" s="13" t="str">
-        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$507,'Dados Mensais (Histórico)'!$B$5:$B$507,E$5,'Dados Mensais (Histórico)'!$E$5:$E$507,$A42))</f>
-        <v/>
-      </c>
-      <c r="G42" s="55">
+        <f>IF(COUNTIFS('Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42)=0,"",SUMIFS('Dados Mensais (Histórico)'!$J$5:$J$518,'Dados Mensais (Histórico)'!$B$5:$B$518,E$5,'Dados Mensais (Histórico)'!$E$5:$E$518,$A42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="41">
         <f>'Preco (R$ x KWh)'!B61</f>
         <v>0</v>
       </c>
-      <c r="H42" s="55">
+      <c r="H42" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -35511,55 +35518,58 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="34" outlineLevel="1"/>
-    <col min="2" max="2" width="40" style="34" customWidth="1"/>
-    <col min="3" max="3" width="16" style="34" customWidth="1"/>
-    <col min="4" max="7" width="12" style="34" customWidth="1"/>
-    <col min="8" max="8" width="14" style="34" customWidth="1"/>
-    <col min="9" max="9" width="16" style="34" customWidth="1"/>
-    <col min="10" max="10" width="14" style="34" customWidth="1"/>
-    <col min="11" max="11" width="18" style="34" customWidth="1"/>
-    <col min="12" max="13" width="16" style="34" customWidth="1"/>
-    <col min="14" max="16384" width="8.7109375" style="34"/>
+    <col min="1" max="1" width="0" style="33" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="2" width="40" style="33" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16" style="33" customWidth="1"/>
+    <col min="4" max="7" width="12" style="33" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="14" style="33" customWidth="1"/>
+    <col min="10" max="10" width="16" style="33" customWidth="1"/>
+    <col min="11" max="11" width="14" style="33" customWidth="1"/>
+    <col min="12" max="12" width="18" style="33" customWidth="1"/>
+    <col min="13" max="14" width="16" style="33" customWidth="1"/>
+    <col min="15" max="16384" width="8.7109375" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="83" t="s">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="79" t="s">
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-    </row>
-    <row r="4" spans="1:13" ht="33.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="34" t="s">
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+    </row>
+    <row r="4" spans="1:14" ht="33.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="33" t="s">
         <v>185</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -35581,26 +35591,29 @@
         <v>87</v>
       </c>
       <c r="H4" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="str">
+    <row r="5" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="33" t="str">
         <f>CONCATENATE(C5,G5)</f>
         <v>703010264346204</v>
       </c>
@@ -35622,27 +35635,28 @@
       <c r="G5" s="12">
         <v>46204</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13">
         <v>338</v>
       </c>
-      <c r="I5" s="13">
+      <c r="J5" s="13">
         <v>0</v>
-      </c>
-      <c r="J5" s="13">
-        <v>338</v>
       </c>
       <c r="K5" s="13">
         <v>338</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="13">
+        <v>338</v>
+      </c>
+      <c r="M5" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M5" s="13">
+      <c r="N5" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="34" t="str">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="str">
         <f t="shared" ref="A6:A22" si="0">CONCATENATE(C6,G6)</f>
         <v>703086904946204</v>
       </c>
@@ -35664,27 +35678,28 @@
       <c r="G6" s="12">
         <v>46204</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="13"/>
+      <c r="I6" s="13">
         <v>875</v>
       </c>
-      <c r="I6" s="13">
+      <c r="J6" s="13">
         <v>0</v>
-      </c>
-      <c r="J6" s="13">
-        <v>875</v>
       </c>
       <c r="K6" s="13">
         <v>875</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="13">
+        <v>875</v>
+      </c>
+      <c r="M6" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="13">
+      <c r="N6" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="34" t="str">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086906546204</v>
       </c>
@@ -35706,27 +35721,28 @@
       <c r="G7" s="12">
         <v>46204</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="13"/>
+      <c r="I7" s="13">
         <v>579</v>
       </c>
-      <c r="I7" s="13">
+      <c r="J7" s="13">
         <v>0</v>
-      </c>
-      <c r="J7" s="13">
-        <v>579</v>
       </c>
       <c r="K7" s="13">
         <v>579</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="13">
+        <v>579</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M7" s="13">
+      <c r="N7" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="34" t="str">
+    <row r="8" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086929446204</v>
       </c>
@@ -35748,27 +35764,28 @@
       <c r="G8" s="12">
         <v>46204</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="13"/>
+      <c r="I8" s="13">
         <v>608</v>
       </c>
-      <c r="I8" s="13">
+      <c r="J8" s="13">
         <v>0</v>
-      </c>
-      <c r="J8" s="13">
-        <v>608</v>
       </c>
       <c r="K8" s="13">
         <v>608</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="13">
+        <v>608</v>
+      </c>
+      <c r="M8" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M8" s="13">
+      <c r="N8" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="34" t="str">
+    <row r="9" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703010264346235</v>
       </c>
@@ -35790,27 +35807,28 @@
       <c r="G9" s="12">
         <v>46235</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="13"/>
+      <c r="I9" s="13">
         <v>3763</v>
       </c>
-      <c r="I9" s="13">
+      <c r="J9" s="13">
         <v>0</v>
       </c>
-      <c r="J9" s="13">
+      <c r="K9" s="13">
         <v>338</v>
       </c>
-      <c r="K9" s="13">
+      <c r="L9" s="13">
         <v>11593.15</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="M9" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="M9" s="13">
+      <c r="N9" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="34" t="str">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086904946235</v>
       </c>
@@ -35832,27 +35850,28 @@
       <c r="G10" s="12">
         <v>46235</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="13"/>
+      <c r="I10" s="13">
         <v>4460</v>
       </c>
-      <c r="I10" s="13">
+      <c r="J10" s="13">
         <v>0</v>
       </c>
-      <c r="J10" s="13">
+      <c r="K10" s="13">
         <v>4460</v>
       </c>
-      <c r="K10" s="13">
+      <c r="L10" s="13">
         <v>875</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="M10" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="13">
+      <c r="N10" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="34" t="str">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086906546235</v>
       </c>
@@ -35866,7 +35885,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>95</v>
@@ -35874,27 +35893,28 @@
       <c r="G11" s="12">
         <v>46235</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="13"/>
+      <c r="I11" s="13">
         <v>3913</v>
       </c>
-      <c r="I11" s="13">
+      <c r="J11" s="13">
         <v>2552</v>
       </c>
-      <c r="J11" s="13">
+      <c r="K11" s="13">
         <v>1361</v>
       </c>
-      <c r="K11" s="13">
+      <c r="L11" s="13">
         <v>579</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="M11" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M11" s="13">
+      <c r="N11" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="34" t="str">
+    <row r="12" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086929446235</v>
       </c>
@@ -35916,27 +35936,28 @@
       <c r="G12" s="12">
         <v>46235</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="13"/>
+      <c r="I12" s="13">
         <v>3930</v>
       </c>
-      <c r="I12" s="13">
+      <c r="J12" s="13">
         <v>3711</v>
       </c>
-      <c r="J12" s="13">
+      <c r="K12" s="13">
         <v>827</v>
       </c>
-      <c r="K12" s="13">
+      <c r="L12" s="13">
         <v>608</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="M12" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M12" s="13">
+      <c r="N12" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="34" t="str">
+    <row r="13" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703010264346266</v>
       </c>
@@ -35958,27 +35979,28 @@
       <c r="G13" s="12">
         <v>46266</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="13"/>
+      <c r="I13" s="13">
         <v>8462</v>
       </c>
-      <c r="I13" s="13">
+      <c r="J13" s="13">
         <v>0</v>
       </c>
-      <c r="J13" s="13">
+      <c r="K13" s="13">
         <v>338</v>
       </c>
-      <c r="K13" s="13">
+      <c r="L13" s="13">
         <v>11593.15</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="M13" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="M13" s="13">
+      <c r="N13" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="34" t="str">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086904946266</v>
       </c>
@@ -36000,27 +36022,28 @@
       <c r="G14" s="12">
         <v>46266</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="13"/>
+      <c r="I14" s="13">
         <v>8831</v>
       </c>
-      <c r="I14" s="13">
+      <c r="J14" s="13">
         <v>0</v>
       </c>
-      <c r="J14" s="13">
+      <c r="K14" s="13">
         <v>8831</v>
       </c>
-      <c r="K14" s="13">
+      <c r="L14" s="13">
         <v>875</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="M14" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M14" s="13">
+      <c r="N14" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="34" t="str">
+    <row r="15" spans="1:14" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="33" t="str">
         <f t="shared" si="0"/>
         <v>703086929446266</v>
       </c>
@@ -36042,172 +36065,208 @@
       <c r="G15" s="12">
         <v>46266</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="13"/>
+      <c r="I15" s="13">
         <v>9082</v>
       </c>
-      <c r="I15" s="13">
+      <c r="J15" s="13">
         <v>7958</v>
       </c>
-      <c r="J15" s="13">
+      <c r="K15" s="13">
         <v>1732</v>
       </c>
-      <c r="K15" s="13">
+      <c r="L15" s="13">
         <v>608</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="M15" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="M15" s="13">
+      <c r="N15" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="34" t="str">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="str">
+        <f t="shared" ref="A16" si="1">CONCATENATE(C16,G16)</f>
+        <v>703086906546266</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="13">
+        <v>60</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="12">
+        <v>46266</v>
+      </c>
+      <c r="H16" s="13">
+        <v>1361</v>
+      </c>
+      <c r="I16" s="13">
+        <v>7136</v>
+      </c>
+      <c r="J16" s="13">
+        <v>4503</v>
+      </c>
+      <c r="K16" s="13">
+        <v>2633</v>
+      </c>
+      <c r="L16" s="13">
+        <v>579</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="38"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="34" t="str">
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="35"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="38"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A18" s="34" t="str">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="35"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="38"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="str">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="35"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="38"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A20" s="34" t="str">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="35"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="38"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="34" t="str">
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="35"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="33" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="38"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A22" s="34" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="38"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="38"/>
-    </row>
-    <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="84" t="s">
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="35"/>
+    </row>
+    <row r="24" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="F24" s="84"/>
-      <c r="G24" s="84"/>
-      <c r="H24" s="84"/>
-      <c r="I24" s="84"/>
-      <c r="J24" s="84"/>
-      <c r="K24" s="84"/>
-      <c r="L24" s="84"/>
-      <c r="M24" s="84"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
     </row>
   </sheetData>
+  <autoFilter ref="B4:N22" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="3">
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B24:M24"/>
+    <mergeCell ref="B1:N1"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B24:N24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -36216,45 +36275,48 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="39.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7109375" style="34"/>
+    <col min="1" max="1" width="36.85546875" style="73" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" style="73" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="73" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="73" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" style="73" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="73" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="73" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="73" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="60.28515625" style="73" customWidth="1"/>
+    <col min="10" max="16384" width="8.7109375" style="73"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="72" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="79" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-    </row>
-    <row r="4" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+    </row>
+    <row r="4" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>67</v>
       </c>
@@ -36265,384 +36327,428 @@
         <v>102</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="74"/>
+      <c r="E5" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="42">
+      <c r="F5" s="75">
         <v>0</v>
       </c>
-      <c r="F5" s="43">
+      <c r="G5" s="76">
         <v>46204</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="H5" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="I5" s="37" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="77"/>
+      <c r="E6" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="46">
+      <c r="F6" s="78">
         <v>1</v>
       </c>
-      <c r="F6" s="47">
+      <c r="G6" s="79">
         <v>46204</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="H6" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="I6" s="38" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="48" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D7" s="80"/>
+      <c r="E7" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="50">
+      <c r="F7" s="81">
         <v>1</v>
       </c>
-      <c r="F7" s="51">
+      <c r="G7" s="82">
         <v>46204</v>
       </c>
-      <c r="G7" s="49" t="s">
+      <c r="H7" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="I7" s="39" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.2">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="74" t="s">
+        <v>187</v>
+      </c>
+      <c r="E8" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="42">
+      <c r="F8" s="75">
         <v>0</v>
       </c>
-      <c r="F8" s="43">
+      <c r="G8" s="76">
         <v>46235</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="H8" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="I8" s="37" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="40" t="s">
+    <row r="9" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="77" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="78">
+        <v>1</v>
+      </c>
+      <c r="G9" s="79">
+        <v>46235</v>
+      </c>
+      <c r="H9" s="77"/>
+      <c r="I9" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B10" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C10" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D10" s="74"/>
+      <c r="E10" s="74" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="42">
+      <c r="F10" s="75">
         <v>0</v>
       </c>
-      <c r="F9" s="43">
+      <c r="G10" s="76">
         <v>46204</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="H10" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="I10" s="37" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="44" t="s">
+    <row r="11" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B11" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C11" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D11" s="77"/>
+      <c r="E11" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="E10" s="46">
+      <c r="F11" s="78">
         <v>0.25</v>
       </c>
-      <c r="F10" s="47">
+      <c r="G11" s="79">
         <v>46204</v>
       </c>
-      <c r="G10" s="45"/>
-      <c r="H10" s="44" t="s">
+      <c r="H11" s="77"/>
+      <c r="I11" s="38" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="44" t="s">
+    <row r="12" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B12" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C12" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D12" s="77"/>
+      <c r="E12" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="46">
+      <c r="F12" s="78">
         <v>0.25</v>
       </c>
-      <c r="F11" s="47">
+      <c r="G12" s="79">
         <v>46204</v>
       </c>
-      <c r="G11" s="45"/>
-      <c r="H11" s="44" t="s">
+      <c r="H12" s="77"/>
+      <c r="I12" s="38" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="44" t="s">
+    <row r="13" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B13" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C13" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D13" s="77"/>
+      <c r="E13" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="46">
+      <c r="F13" s="78">
         <v>0.25</v>
       </c>
-      <c r="F12" s="47">
+      <c r="G13" s="79">
         <v>46204</v>
       </c>
-      <c r="G12" s="45"/>
-      <c r="H12" s="44" t="s">
+      <c r="H13" s="77"/>
+      <c r="I13" s="38" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="44" t="s">
+    <row r="14" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B14" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C14" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D14" s="77"/>
+      <c r="E14" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="E13" s="46">
+      <c r="F14" s="78">
         <v>0.25</v>
       </c>
-      <c r="F13" s="47">
+      <c r="G14" s="79">
         <v>46204</v>
       </c>
-      <c r="G13" s="45"/>
-      <c r="H13" s="44" t="s">
+      <c r="H14" s="77"/>
+      <c r="I14" s="38" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="90" x14ac:dyDescent="0.2">
-      <c r="A14" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="46">
-        <v>1</v>
-      </c>
-      <c r="F14" s="47">
-        <v>46235</v>
-      </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="44" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="14" t="s">
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="85"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B17" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="35"/>
-      <c r="D16" s="35"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="14" t="s">
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B18" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="14" t="s">
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="14" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="14"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="14"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="53" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="14"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="87" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="86" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="86"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="87" t="s">
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
-      <c r="D23" s="87"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="88" t="s">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="90" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="85" t="s">
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="91" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
+      <c r="D26" s="91"/>
+      <c r="E26" s="91"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I20" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -36651,67 +36757,67 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="34" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="34" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="34" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="34" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="34" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="34" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="34" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.7109375" style="34"/>
+    <col min="1" max="1" width="36.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="33" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="33" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="33" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="33" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.7109375" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
     </row>
     <row r="4" spans="1:16" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -36770,7 +36876,7 @@
       <c r="B5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="89" t="s">
+      <c r="C5" s="46" t="s">
         <v>176</v>
       </c>
       <c r="D5" s="11" t="s">
@@ -36820,7 +36926,7 @@
       <c r="B6" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="89" t="s">
+      <c r="C6" s="46" t="s">
         <v>176</v>
       </c>
       <c r="D6" s="11" t="s">
@@ -36918,7 +37024,7 @@
       <c r="B8" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="46" t="s">
         <v>177</v>
       </c>
       <c r="D8" s="11" t="s">
@@ -36968,7 +37074,9 @@
       <c r="B9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="46" t="s">
+        <v>187</v>
+      </c>
       <c r="D9" s="11" t="s">
         <v>128</v>
       </c>
@@ -37016,7 +37124,7 @@
       <c r="B10" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="89" t="s">
+      <c r="C10" s="46" t="s">
         <v>178</v>
       </c>
       <c r="D10" s="11" t="s">
@@ -37066,7 +37174,7 @@
       <c r="B11" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C11" s="46" t="s">
         <v>179</v>
       </c>
       <c r="D11" s="11" t="s">
@@ -37116,7 +37224,7 @@
       <c r="B12" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="89" t="s">
+      <c r="C12" s="46" t="s">
         <v>180</v>
       </c>
       <c r="D12" s="11" t="s">
@@ -37166,7 +37274,7 @@
       <c r="B13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="46" t="s">
         <v>181</v>
       </c>
       <c r="D13" s="11" t="s">
@@ -37216,7 +37324,7 @@
       <c r="B14" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="46" t="s">
         <v>182</v>
       </c>
       <c r="D14" s="11" t="s">
@@ -37266,7 +37374,7 @@
       <c r="B15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="46" t="s">
         <v>176</v>
       </c>
       <c r="D15" s="11" t="s">
@@ -37364,7 +37472,7 @@
       <c r="B17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="89" t="s">
+      <c r="C17" s="46" t="s">
         <v>177</v>
       </c>
       <c r="D17" s="11" t="s">
@@ -37414,30 +37522,32 @@
       <c r="B18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="46" t="s">
+        <v>187</v>
+      </c>
       <c r="D18" s="11" t="s">
         <v>128</v>
       </c>
       <c r="E18" s="12">
-        <v>46235</v>
+        <v>46204</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>127</v>
       </c>
       <c r="G18" s="13">
-        <v>579</v>
+        <v>0</v>
       </c>
       <c r="H18" s="13">
         <v>0</v>
       </c>
       <c r="I18" s="13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J18" s="13">
-        <v>3334</v>
+        <v>579</v>
       </c>
       <c r="K18" s="13">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="L18" s="13">
         <v>0</v>
@@ -37455,18 +37565,18 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="89" t="s">
-        <v>178</v>
+        <v>48</v>
+      </c>
+      <c r="C19" s="46" t="s">
+        <v>187</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E19" s="12">
         <v>46235</v>
@@ -37475,7 +37585,7 @@
         <v>127</v>
       </c>
       <c r="G19" s="13">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="H19" s="13">
         <v>0</v>
@@ -37484,7 +37594,7 @@
         <v>6</v>
       </c>
       <c r="J19" s="13">
-        <v>3322</v>
+        <v>3334</v>
       </c>
       <c r="K19" s="13">
         <v>0</v>
@@ -37499,7 +37609,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="13">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="P19" s="11" t="s">
         <v>95</v>
@@ -37510,16 +37620,16 @@
         <v>49</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="89" t="s">
-        <v>179</v>
+        <v>50</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>178</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E20" s="12">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>127</v>
@@ -37531,19 +37641,19 @@
         <v>0</v>
       </c>
       <c r="I20" s="13">
-        <v>792</v>
+        <v>6</v>
       </c>
       <c r="J20" s="13">
+        <v>3322</v>
+      </c>
+      <c r="K20" s="13">
         <v>0</v>
       </c>
-      <c r="K20" s="13">
-        <v>152</v>
-      </c>
       <c r="L20" s="13">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M20" s="13">
-        <v>640</v>
+        <v>100</v>
       </c>
       <c r="N20" s="13">
         <v>0</v>
@@ -37560,10 +37670,10 @@
         <v>49</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="89" t="s">
-        <v>180</v>
+        <v>76</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>179</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>74</v>
@@ -37581,7 +37691,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="13">
-        <v>518</v>
+        <v>792</v>
       </c>
       <c r="J21" s="13">
         <v>0</v>
@@ -37593,7 +37703,7 @@
         <v>152</v>
       </c>
       <c r="M21" s="13">
-        <v>366</v>
+        <v>640</v>
       </c>
       <c r="N21" s="13">
         <v>0</v>
@@ -37610,10 +37720,10 @@
         <v>49</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="89" t="s">
-        <v>181</v>
+        <v>77</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>180</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>74</v>
@@ -37631,7 +37741,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="13">
-        <v>355</v>
+        <v>518</v>
       </c>
       <c r="J22" s="13">
         <v>0</v>
@@ -37643,7 +37753,7 @@
         <v>152</v>
       </c>
       <c r="M22" s="13">
-        <v>203</v>
+        <v>366</v>
       </c>
       <c r="N22" s="13">
         <v>0</v>
@@ -37660,10 +37770,10 @@
         <v>49</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="89" t="s">
-        <v>182</v>
+        <v>78</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>181</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>74</v>
@@ -37681,7 +37791,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="13">
-        <v>585</v>
+        <v>355</v>
       </c>
       <c r="J23" s="13">
         <v>0</v>
@@ -37693,7 +37803,7 @@
         <v>152</v>
       </c>
       <c r="M23" s="13">
-        <v>433</v>
+        <v>203</v>
       </c>
       <c r="N23" s="13">
         <v>0</v>
@@ -37707,19 +37817,19 @@
     </row>
     <row r="24" spans="1:16" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="89" t="s">
-        <v>176</v>
+        <v>79</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>182</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="E24" s="12">
-        <v>46266</v>
+        <v>46204</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>127</v>
@@ -37731,19 +37841,19 @@
         <v>0</v>
       </c>
       <c r="I24" s="13">
-        <v>4</v>
+        <v>585</v>
       </c>
       <c r="J24" s="13">
-        <v>4699</v>
+        <v>0</v>
       </c>
       <c r="K24" s="13">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L24" s="13">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M24" s="13">
-        <v>100</v>
+        <v>433</v>
       </c>
       <c r="N24" s="13">
         <v>0</v>
@@ -37760,11 +37870,13 @@
         <v>41</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="11"/>
+        <v>42</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>176</v>
+      </c>
       <c r="D25" s="11" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E25" s="12">
         <v>46266</v>
@@ -37776,22 +37888,22 @@
         <v>0</v>
       </c>
       <c r="H25" s="13">
-        <v>2800.35</v>
+        <v>0</v>
       </c>
       <c r="I25" s="13">
-        <v>13119</v>
+        <v>4</v>
       </c>
       <c r="J25" s="13">
+        <v>4699</v>
+      </c>
+      <c r="K25" s="13">
         <v>0</v>
       </c>
-      <c r="K25" s="13">
-        <v>4699</v>
-      </c>
       <c r="L25" s="13">
-        <v>7499.35</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13">
-        <v>5619.65</v>
+        <v>100</v>
       </c>
       <c r="N25" s="13">
         <v>0</v>
@@ -37803,18 +37915,16 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="22.5" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="89" t="s">
-        <v>177</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="C26" s="11"/>
       <c r="D26" s="11" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="E26" s="12">
         <v>46266</v>
@@ -37823,48 +37933,48 @@
         <v>127</v>
       </c>
       <c r="G26" s="13">
-        <v>4460</v>
+        <v>0</v>
       </c>
       <c r="H26" s="13">
+        <v>2800.35</v>
+      </c>
+      <c r="I26" s="13">
+        <v>13119</v>
+      </c>
+      <c r="J26" s="13">
         <v>0</v>
       </c>
-      <c r="I26" s="13">
-        <v>0</v>
-      </c>
-      <c r="J26" s="13">
-        <v>4371</v>
-      </c>
       <c r="K26" s="13">
-        <v>4371</v>
+        <v>4699</v>
       </c>
       <c r="L26" s="13">
-        <v>0</v>
+        <v>7499.35</v>
       </c>
       <c r="M26" s="13">
-        <v>100</v>
+        <v>5619.65</v>
       </c>
       <c r="N26" s="13">
         <v>0</v>
       </c>
       <c r="O26" s="13">
-        <v>8831</v>
+        <v>0</v>
       </c>
       <c r="P26" s="11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="89" t="s">
-        <v>178</v>
+        <v>45</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>177</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E27" s="12">
         <v>46266</v>
@@ -37873,19 +37983,19 @@
         <v>127</v>
       </c>
       <c r="G27" s="13">
-        <v>0</v>
+        <v>4460</v>
       </c>
       <c r="H27" s="13">
         <v>0</v>
       </c>
       <c r="I27" s="13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J27" s="13">
-        <v>5152</v>
+        <v>4371</v>
       </c>
       <c r="K27" s="13">
-        <v>0</v>
+        <v>4371</v>
       </c>
       <c r="L27" s="13">
         <v>0</v>
@@ -37897,7 +38007,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="13">
-        <v>0</v>
+        <v>8831</v>
       </c>
       <c r="P27" s="11" t="s">
         <v>95</v>
@@ -37908,16 +38018,16 @@
         <v>49</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="89" t="s">
-        <v>180</v>
+        <v>50</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>178</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E28" s="12">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>127</v>
@@ -37929,25 +38039,25 @@
         <v>0</v>
       </c>
       <c r="I28" s="13">
-        <v>758</v>
+        <v>8</v>
       </c>
       <c r="J28" s="13">
+        <v>5152</v>
+      </c>
+      <c r="K28" s="13">
         <v>0</v>
       </c>
-      <c r="K28" s="13">
-        <v>830.5</v>
-      </c>
       <c r="L28" s="13">
-        <v>758</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N28" s="13">
         <v>0</v>
       </c>
       <c r="O28" s="13">
-        <v>72.5</v>
+        <v>0</v>
       </c>
       <c r="P28" s="11" t="s">
         <v>95</v>
@@ -37960,35 +38070,35 @@
       <c r="B29" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="89" t="s">
+      <c r="C29" s="46" t="s">
         <v>180</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E29" s="12">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>127</v>
       </c>
       <c r="G29" s="13">
-        <v>72.5</v>
+        <v>0</v>
       </c>
       <c r="H29" s="13">
         <v>0</v>
       </c>
       <c r="I29" s="13">
-        <v>1301</v>
+        <v>758</v>
       </c>
       <c r="J29" s="13">
         <v>0</v>
       </c>
       <c r="K29" s="13">
-        <v>1288</v>
+        <v>830.5</v>
       </c>
       <c r="L29" s="13">
-        <v>1301</v>
+        <v>758</v>
       </c>
       <c r="M29" s="13">
         <v>0</v>
@@ -37997,7 +38107,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="13">
-        <v>59.5</v>
+        <v>72.5</v>
       </c>
       <c r="P29" s="11" t="s">
         <v>95</v>
@@ -38008,46 +38118,46 @@
         <v>49</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="89" t="s">
-        <v>179</v>
+        <v>77</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>180</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E30" s="12">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>127</v>
       </c>
       <c r="G30" s="13">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="H30" s="13">
         <v>0</v>
       </c>
       <c r="I30" s="13">
-        <v>1221</v>
+        <v>1301</v>
       </c>
       <c r="J30" s="13">
         <v>0</v>
       </c>
       <c r="K30" s="13">
-        <v>830.5</v>
+        <v>1288</v>
       </c>
       <c r="L30" s="13">
-        <v>830.5</v>
+        <v>1301</v>
       </c>
       <c r="M30" s="13">
-        <v>390.5</v>
+        <v>0</v>
       </c>
       <c r="N30" s="13">
         <v>0</v>
       </c>
       <c r="O30" s="13">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="P30" s="11" t="s">
         <v>95</v>
@@ -38060,14 +38170,14 @@
       <c r="B31" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="89" t="s">
+      <c r="C31" s="46" t="s">
         <v>179</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E31" s="12">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>127</v>
@@ -38079,25 +38189,25 @@
         <v>0</v>
       </c>
       <c r="I31" s="13">
-        <v>972</v>
+        <v>1221</v>
       </c>
       <c r="J31" s="13">
         <v>0</v>
       </c>
       <c r="K31" s="13">
-        <v>1288</v>
+        <v>830.5</v>
       </c>
       <c r="L31" s="13">
-        <v>972</v>
+        <v>830.5</v>
       </c>
       <c r="M31" s="13">
-        <v>0</v>
+        <v>390.5</v>
       </c>
       <c r="N31" s="13">
         <v>0</v>
       </c>
       <c r="O31" s="13">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="P31" s="11" t="s">
         <v>95</v>
@@ -38108,16 +38218,16 @@
         <v>49</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="89" t="s">
-        <v>181</v>
+        <v>76</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>179</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E32" s="12">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>127</v>
@@ -38129,25 +38239,25 @@
         <v>0</v>
       </c>
       <c r="I32" s="13">
-        <v>1065</v>
+        <v>972</v>
       </c>
       <c r="J32" s="13">
         <v>0</v>
       </c>
       <c r="K32" s="13">
-        <v>830.5</v>
+        <v>1288</v>
       </c>
       <c r="L32" s="13">
-        <v>830.5</v>
+        <v>972</v>
       </c>
       <c r="M32" s="13">
-        <v>234.5</v>
+        <v>0</v>
       </c>
       <c r="N32" s="13">
         <v>0</v>
       </c>
       <c r="O32" s="13">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="P32" s="11" t="s">
         <v>95</v>
@@ -38160,14 +38270,14 @@
       <c r="B33" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="C33" s="46" t="s">
         <v>181</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E33" s="12">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>127</v>
@@ -38179,25 +38289,25 @@
         <v>0</v>
       </c>
       <c r="I33" s="13">
-        <v>966</v>
+        <v>1065</v>
       </c>
       <c r="J33" s="13">
         <v>0</v>
       </c>
       <c r="K33" s="13">
-        <v>1288</v>
+        <v>830.5</v>
       </c>
       <c r="L33" s="13">
-        <v>966</v>
+        <v>830.5</v>
       </c>
       <c r="M33" s="13">
-        <v>0</v>
+        <v>234.5</v>
       </c>
       <c r="N33" s="13">
         <v>0</v>
       </c>
       <c r="O33" s="13">
-        <v>322</v>
+        <v>0</v>
       </c>
       <c r="P33" s="11" t="s">
         <v>95</v>
@@ -38208,16 +38318,16 @@
         <v>49</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C34" s="89" t="s">
-        <v>182</v>
+        <v>78</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>181</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E34" s="12">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>127</v>
@@ -38229,16 +38339,16 @@
         <v>0</v>
       </c>
       <c r="I34" s="13">
-        <v>684</v>
+        <v>966</v>
       </c>
       <c r="J34" s="13">
         <v>0</v>
       </c>
       <c r="K34" s="13">
-        <v>830.5</v>
+        <v>1288</v>
       </c>
       <c r="L34" s="13">
-        <v>684</v>
+        <v>966</v>
       </c>
       <c r="M34" s="13">
         <v>0</v>
@@ -38247,7 +38357,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="13">
-        <v>146.5</v>
+        <v>322</v>
       </c>
       <c r="P34" s="11" t="s">
         <v>95</v>
@@ -38260,14 +38370,14 @@
       <c r="B35" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="89" t="s">
+      <c r="C35" s="46" t="s">
         <v>182</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>74</v>
       </c>
       <c r="E35" s="12">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>127</v>
@@ -38279,16 +38389,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="13">
-        <v>1008</v>
+        <v>684</v>
       </c>
       <c r="J35" s="13">
         <v>0</v>
       </c>
       <c r="K35" s="13">
-        <v>1288</v>
+        <v>830.5</v>
       </c>
       <c r="L35" s="13">
-        <v>1008</v>
+        <v>684</v>
       </c>
       <c r="M35" s="13">
         <v>0</v>
@@ -38297,56 +38407,384 @@
         <v>0</v>
       </c>
       <c r="O35" s="13">
-        <v>426.5</v>
+        <v>146.5</v>
       </c>
       <c r="P35" s="11" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A36" s="9"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="11"/>
+    <row r="36" spans="1:16" ht="22.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="12">
+        <v>46266</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="13">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13">
+        <v>1008</v>
+      </c>
+      <c r="J36" s="13">
+        <v>0</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1288</v>
+      </c>
+      <c r="L36" s="13">
+        <v>1008</v>
+      </c>
+      <c r="M36" s="13">
+        <v>0</v>
+      </c>
+      <c r="N36" s="13">
+        <v>0</v>
+      </c>
+      <c r="O36" s="13">
+        <v>426.5</v>
+      </c>
+      <c r="P36" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E37" s="12">
+        <v>46266</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="13">
+        <v>579</v>
+      </c>
+      <c r="H37" s="13">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13">
+        <v>0</v>
+      </c>
+      <c r="J37" s="13">
+        <v>3223</v>
+      </c>
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13">
+        <v>100</v>
+      </c>
+      <c r="N37" s="13">
+        <v>0</v>
+      </c>
+      <c r="O37" s="13">
+        <v>579</v>
+      </c>
+      <c r="P37" s="11" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A38" s="79" t="s">
+      <c r="A38" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="12">
+        <v>46235</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G38" s="13">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13">
+        <v>0</v>
+      </c>
+      <c r="I38" s="13">
+        <v>2552</v>
+      </c>
+      <c r="J38" s="13">
+        <v>0</v>
+      </c>
+      <c r="K38" s="13">
+        <v>3334</v>
+      </c>
+      <c r="L38" s="13">
+        <v>2552</v>
+      </c>
+      <c r="M38" s="13">
+        <v>0</v>
+      </c>
+      <c r="N38" s="13">
+        <v>0</v>
+      </c>
+      <c r="O38" s="13">
+        <f>K38-L38</f>
+        <v>782</v>
+      </c>
+      <c r="P38" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E39" s="12">
+        <v>46266</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G39" s="13">
+        <v>782</v>
+      </c>
+      <c r="H39" s="13">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13">
+        <v>1951</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="13">
+        <v>3223</v>
+      </c>
+      <c r="L39" s="13">
+        <v>1951</v>
+      </c>
+      <c r="M39" s="13">
+        <v>0</v>
+      </c>
+      <c r="N39" s="13">
+        <v>0</v>
+      </c>
+      <c r="O39" s="13">
+        <f>G39+K39-L39</f>
+        <v>2054</v>
+      </c>
+      <c r="P39" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A40" s="9"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="11"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A41" s="9"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+      <c r="M41" s="13"/>
+      <c r="N41" s="13"/>
+      <c r="O41" s="13"/>
+      <c r="P41" s="11"/>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A42" s="9"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+      <c r="M42" s="13"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="13"/>
+      <c r="P42" s="11"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="9"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="11"/>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A44" s="9"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="11"/>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A45" s="9"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="11"/>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A46" s="9"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="13"/>
+      <c r="M46" s="13"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="13"/>
+      <c r="P46" s="11"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A47" s="9"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="11"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="79"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="79"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="79"/>
-      <c r="N38" s="79"/>
-      <c r="O38" s="79"/>
-      <c r="P38" s="79"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="66"/>
+      <c r="M49" s="66"/>
+      <c r="N49" s="66"/>
+      <c r="O49" s="66"/>
+      <c r="P49" s="66"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P35" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
+  <autoFilter ref="A4:P39" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A49:P49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -38358,33 +38796,33 @@
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="34" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7109375" style="34"/>
+    <col min="1" max="1" width="11.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.7109375" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="65" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="66" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -38422,23 +38860,23 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
-        <f>_xlfn.MINIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$H$5:$H$500,"&lt;&gt;")</f>
+        <f>_xlfn.MINIFS('Resumo Usinas (Histórico)'!$G$5:$G$500,'Resumo Usinas (Histórico)'!$I$5:$I$500,"&lt;&gt;")</f>
         <v>46204</v>
       </c>
       <c r="B6" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
         <v>338</v>
       </c>
       <c r="C6" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
         <v>875</v>
       </c>
       <c r="D6" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
         <v>579</v>
       </c>
       <c r="E6" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A6))</f>
         <v>608</v>
       </c>
     </row>
@@ -38448,19 +38886,19 @@
         <v>46235</v>
       </c>
       <c r="B7" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
         <v>338</v>
       </c>
       <c r="C7" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
         <v>4460</v>
       </c>
       <c r="D7" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
         <v>1361</v>
       </c>
       <c r="E7" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A7))</f>
         <v>827</v>
       </c>
     </row>
@@ -38470,19 +38908,19 @@
         <v>46266</v>
       </c>
       <c r="B8" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
         <v>338</v>
       </c>
       <c r="C8" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
         <v>8831</v>
       </c>
-      <c r="D8" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
-        <v/>
+      <c r="D8" s="13">
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
+        <v>2633</v>
       </c>
       <c r="E8" s="13">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A8))</f>
         <v>1732</v>
       </c>
     </row>
@@ -38492,19 +38930,19 @@
         <v>46296</v>
       </c>
       <c r="B9" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
         <v/>
       </c>
       <c r="C9" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
         <v/>
       </c>
       <c r="D9" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
         <v/>
       </c>
       <c r="E9" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A9))</f>
         <v/>
       </c>
     </row>
@@ -38514,19 +38952,19 @@
         <v>46327</v>
       </c>
       <c r="B10" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
         <v/>
       </c>
       <c r="C10" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
         <v/>
       </c>
       <c r="D10" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
         <v/>
       </c>
       <c r="E10" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A10))</f>
         <v/>
       </c>
     </row>
@@ -38536,19 +38974,19 @@
         <v>46357</v>
       </c>
       <c r="B11" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
         <v/>
       </c>
       <c r="C11" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
         <v/>
       </c>
       <c r="D11" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
         <v/>
       </c>
       <c r="E11" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A11))</f>
         <v/>
       </c>
     </row>
@@ -38558,19 +38996,19 @@
         <v>46388</v>
       </c>
       <c r="B12" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
         <v/>
       </c>
       <c r="C12" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
         <v/>
       </c>
       <c r="D12" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
         <v/>
       </c>
       <c r="E12" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A12))</f>
         <v/>
       </c>
     </row>
@@ -38580,19 +39018,19 @@
         <v>46419</v>
       </c>
       <c r="B13" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
         <v/>
       </c>
       <c r="C13" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
         <v/>
       </c>
       <c r="D13" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
         <v/>
       </c>
       <c r="E13" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A13))</f>
         <v/>
       </c>
     </row>
@@ -38602,19 +39040,19 @@
         <v>46447</v>
       </c>
       <c r="B14" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
         <v/>
       </c>
       <c r="C14" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
         <v/>
       </c>
       <c r="D14" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
         <v/>
       </c>
       <c r="E14" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A14))</f>
         <v/>
       </c>
     </row>
@@ -38624,19 +39062,19 @@
         <v>46478</v>
       </c>
       <c r="B15" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
         <v/>
       </c>
       <c r="C15" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
         <v/>
       </c>
       <c r="D15" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
         <v/>
       </c>
       <c r="E15" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A15))</f>
         <v/>
       </c>
     </row>
@@ -38646,19 +39084,19 @@
         <v>46508</v>
       </c>
       <c r="B16" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
         <v/>
       </c>
       <c r="C16" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
         <v/>
       </c>
       <c r="D16" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
         <v/>
       </c>
       <c r="E16" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A16))</f>
         <v/>
       </c>
     </row>
@@ -38668,19 +39106,19 @@
         <v>46539</v>
       </c>
       <c r="B17" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
         <v/>
       </c>
       <c r="C17" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
         <v/>
       </c>
       <c r="D17" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
         <v/>
       </c>
       <c r="E17" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A17))</f>
         <v/>
       </c>
     </row>
@@ -38690,19 +39128,19 @@
         <v>46569</v>
       </c>
       <c r="B18" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
         <v/>
       </c>
       <c r="C18" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
         <v/>
       </c>
       <c r="D18" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
         <v/>
       </c>
       <c r="E18" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A18))</f>
         <v/>
       </c>
     </row>
@@ -38712,19 +39150,19 @@
         <v>46600</v>
       </c>
       <c r="B19" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
         <v/>
       </c>
       <c r="C19" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
         <v/>
       </c>
       <c r="D19" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
         <v/>
       </c>
       <c r="E19" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A19))</f>
         <v/>
       </c>
     </row>
@@ -38734,19 +39172,19 @@
         <v>46631</v>
       </c>
       <c r="B20" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
         <v/>
       </c>
       <c r="C20" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
         <v/>
       </c>
       <c r="D20" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
         <v/>
       </c>
       <c r="E20" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A20))</f>
         <v/>
       </c>
     </row>
@@ -38756,19 +39194,19 @@
         <v>46661</v>
       </c>
       <c r="B21" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
         <v/>
       </c>
       <c r="C21" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
         <v/>
       </c>
       <c r="D21" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
         <v/>
       </c>
       <c r="E21" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A21))</f>
         <v/>
       </c>
     </row>
@@ -38778,19 +39216,19 @@
         <v>46692</v>
       </c>
       <c r="B22" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
         <v/>
       </c>
       <c r="C22" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
         <v/>
       </c>
       <c r="D22" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
         <v/>
       </c>
       <c r="E22" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A22))</f>
         <v/>
       </c>
     </row>
@@ -38800,19 +39238,19 @@
         <v>46722</v>
       </c>
       <c r="B23" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
         <v/>
       </c>
       <c r="C23" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
         <v/>
       </c>
       <c r="D23" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
         <v/>
       </c>
       <c r="E23" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A23))</f>
         <v/>
       </c>
     </row>
@@ -38822,19 +39260,19 @@
         <v>46753</v>
       </c>
       <c r="B24" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
         <v/>
       </c>
       <c r="C24" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
         <v/>
       </c>
       <c r="D24" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
         <v/>
       </c>
       <c r="E24" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A24))</f>
         <v/>
       </c>
     </row>
@@ -38844,19 +39282,19 @@
         <v>46784</v>
       </c>
       <c r="B25" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
         <v/>
       </c>
       <c r="C25" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
         <v/>
       </c>
       <c r="D25" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
         <v/>
       </c>
       <c r="E25" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A25))</f>
         <v/>
       </c>
     </row>
@@ -38866,19 +39304,19 @@
         <v>46813</v>
       </c>
       <c r="B26" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
         <v/>
       </c>
       <c r="C26" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
         <v/>
       </c>
       <c r="D26" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
         <v/>
       </c>
       <c r="E26" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A26))</f>
         <v/>
       </c>
     </row>
@@ -38888,19 +39326,19 @@
         <v>46844</v>
       </c>
       <c r="B27" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
         <v/>
       </c>
       <c r="C27" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
         <v/>
       </c>
       <c r="D27" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
         <v/>
       </c>
       <c r="E27" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A27))</f>
         <v/>
       </c>
     </row>
@@ -38910,19 +39348,19 @@
         <v>46874</v>
       </c>
       <c r="B28" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
         <v/>
       </c>
       <c r="C28" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
         <v/>
       </c>
       <c r="D28" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
         <v/>
       </c>
       <c r="E28" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A28))</f>
         <v/>
       </c>
     </row>
@@ -38932,19 +39370,19 @@
         <v>46905</v>
       </c>
       <c r="B29" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
         <v/>
       </c>
       <c r="C29" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
         <v/>
       </c>
       <c r="D29" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
         <v/>
       </c>
       <c r="E29" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A29))</f>
         <v/>
       </c>
     </row>
@@ -38954,19 +39392,19 @@
         <v>46935</v>
       </c>
       <c r="B30" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
         <v/>
       </c>
       <c r="C30" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
         <v/>
       </c>
       <c r="D30" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
         <v/>
       </c>
       <c r="E30" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A30))</f>
         <v/>
       </c>
     </row>
@@ -38976,19 +39414,19 @@
         <v>46966</v>
       </c>
       <c r="B31" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
         <v/>
       </c>
       <c r="C31" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
         <v/>
       </c>
       <c r="D31" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
         <v/>
       </c>
       <c r="E31" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A31))</f>
         <v/>
       </c>
     </row>
@@ -38998,19 +39436,19 @@
         <v>46997</v>
       </c>
       <c r="B32" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
         <v/>
       </c>
       <c r="C32" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
         <v/>
       </c>
       <c r="D32" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
         <v/>
       </c>
       <c r="E32" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A32))</f>
         <v/>
       </c>
     </row>
@@ -39020,19 +39458,19 @@
         <v>47027</v>
       </c>
       <c r="B33" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
         <v/>
       </c>
       <c r="C33" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
         <v/>
       </c>
       <c r="D33" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
         <v/>
       </c>
       <c r="E33" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A33))</f>
         <v/>
       </c>
     </row>
@@ -39042,19 +39480,19 @@
         <v>47058</v>
       </c>
       <c r="B34" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
         <v/>
       </c>
       <c r="C34" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
         <v/>
       </c>
       <c r="D34" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
         <v/>
       </c>
       <c r="E34" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A34))</f>
         <v/>
       </c>
     </row>
@@ -39064,19 +39502,19 @@
         <v>47088</v>
       </c>
       <c r="B35" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
         <v/>
       </c>
       <c r="C35" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
         <v/>
       </c>
       <c r="D35" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
         <v/>
       </c>
       <c r="E35" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A35))</f>
         <v/>
       </c>
     </row>
@@ -39086,19 +39524,19 @@
         <v>47119</v>
       </c>
       <c r="B36" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
         <v/>
       </c>
       <c r="C36" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
         <v/>
       </c>
       <c r="D36" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
         <v/>
       </c>
       <c r="E36" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A36))</f>
         <v/>
       </c>
     </row>
@@ -39108,19 +39546,19 @@
         <v>47150</v>
       </c>
       <c r="B37" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
         <v/>
       </c>
       <c r="C37" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
         <v/>
       </c>
       <c r="D37" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
         <v/>
       </c>
       <c r="E37" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A37))</f>
         <v/>
       </c>
     </row>
@@ -39130,19 +39568,19 @@
         <v>47178</v>
       </c>
       <c r="B38" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
         <v/>
       </c>
       <c r="C38" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
         <v/>
       </c>
       <c r="D38" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
         <v/>
       </c>
       <c r="E38" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A38))</f>
         <v/>
       </c>
     </row>
@@ -39152,19 +39590,19 @@
         <v>47209</v>
       </c>
       <c r="B39" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
         <v/>
       </c>
       <c r="C39" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
         <v/>
       </c>
       <c r="D39" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
         <v/>
       </c>
       <c r="E39" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A39))</f>
         <v/>
       </c>
     </row>
@@ -39174,19 +39612,19 @@
         <v>47239</v>
       </c>
       <c r="B40" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
         <v/>
       </c>
       <c r="C40" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
         <v/>
       </c>
       <c r="D40" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
         <v/>
       </c>
       <c r="E40" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A40))</f>
         <v/>
       </c>
     </row>
@@ -39196,19 +39634,19 @@
         <v>47270</v>
       </c>
       <c r="B41" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030102643",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
         <v/>
       </c>
       <c r="C41" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869049",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
         <v/>
       </c>
       <c r="D41" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869065",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
         <v/>
       </c>
       <c r="E41" s="13" t="str">
-        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$J$5:$J$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
+        <f>IF(COUNTIFS('Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41)=0,"",SUMIFS('Resumo Usinas (Histórico)'!$K$5:$K$500,'Resumo Usinas (Histórico)'!$C$5:$C$500,"7030869294",'Resumo Usinas (Histórico)'!$G$5:$G$500,A41))</f>
         <v/>
       </c>
     </row>
